--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 1.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 1.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07137AAE-3105-48A0-916D-CDF463912086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -226,7 +225,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -491,9 +490,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -531,9 +530,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -568,7 +567,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -603,7 +602,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -776,7 +775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -871,13 +870,34 @@
       <c r="E4" s="20">
         <v>45048</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="19"/>
+      <c r="F4" s="17" t="str">
+        <f>VLOOKUP(LEFT(C4,3),$C$17:$E$21,2,FALSE)</f>
+        <v>JAKARTA - SURABAYA</v>
+      </c>
+      <c r="G4" s="17">
+        <f>VLOOKUP(LEFT(C4,3),$C$17:$E$21,3,FALSE)</f>
+        <v>400000</v>
+      </c>
+      <c r="H4" s="17" t="str">
+        <f>INDEX($F$17:$F$20,MATCH(MID(C4,4,1),$G$17:$G$20,0),0)</f>
+        <v>BISNIS</v>
+      </c>
+      <c r="I4" s="18" t="str">
+        <f>HLOOKUP(MID(C4,6,2),$I$17:$L$19,2,FALSE)</f>
+        <v>PAKET A</v>
+      </c>
+      <c r="J4" s="18">
+        <f>HLOOKUP(MID(C4,6,2),$I$17:$L$19,3,FALSE)</f>
+        <v>100000</v>
+      </c>
+      <c r="K4" s="18">
+        <f>IF($E$2-E4&gt;30,INDEX($H$17:$H$20,MATCH(H4,$F$17:$F$20,0))*G4,0)</f>
+        <v>40000</v>
+      </c>
+      <c r="L4" s="19">
+        <f>G4+J4-M4</f>
+        <v>500000</v>
+      </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
@@ -892,13 +912,34 @@
       <c r="E5" s="20">
         <v>45051</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="19"/>
+      <c r="F5" s="17" t="str">
+        <f t="shared" ref="F5:F13" si="0">VLOOKUP(LEFT(C5,3),$C$17:$E$21,2,FALSE)</f>
+        <v>JAKARTA - BALI</v>
+      </c>
+      <c r="G5" s="17">
+        <f t="shared" ref="G5:G13" si="1">VLOOKUP(LEFT(C5,3),$C$17:$E$21,3,FALSE)</f>
+        <v>600000</v>
+      </c>
+      <c r="H5" s="17" t="str">
+        <f t="shared" ref="H5:H13" si="2">INDEX($F$17:$F$20,MATCH(MID(C5,4,1),$G$17:$G$20,0),0)</f>
+        <v>BISNIS</v>
+      </c>
+      <c r="I5" s="18" t="str">
+        <f t="shared" ref="I5:I13" si="3">HLOOKUP(MID(C5,6,2),$I$17:$L$19,2,FALSE)</f>
+        <v>PAKET C</v>
+      </c>
+      <c r="J5" s="18">
+        <f t="shared" ref="J5:J13" si="4">HLOOKUP(MID(C5,6,2),$I$17:$L$19,3,FALSE)</f>
+        <v>50000</v>
+      </c>
+      <c r="K5" s="18">
+        <f t="shared" ref="K5:K13" si="5">IF($E$2-E5&gt;30,INDEX($H$17:$H$20,MATCH(H5,$F$17:$F$20,0))*G5,0)</f>
+        <v>60000</v>
+      </c>
+      <c r="L5" s="19">
+        <f t="shared" ref="L5:L13" si="6">G5+J5-M5</f>
+        <v>650000</v>
+      </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
@@ -913,13 +954,34 @@
       <c r="E6" s="20">
         <v>45057</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="19"/>
+      <c r="F6" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - BANDUNG</v>
+      </c>
+      <c r="G6" s="17">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="H6" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>EKONOMI</v>
+      </c>
+      <c r="I6" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET C</v>
+      </c>
+      <c r="J6" s="18">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="K6" s="18">
+        <f t="shared" si="5"/>
+        <v>15000</v>
+      </c>
+      <c r="L6" s="19">
+        <f t="shared" si="6"/>
+        <v>350000</v>
+      </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -934,13 +996,34 @@
       <c r="E7" s="20">
         <v>45059</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
+      <c r="F7" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - BANDUNG</v>
+      </c>
+      <c r="G7" s="17">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="H7" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>EKONOMI</v>
+      </c>
+      <c r="I7" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET B</v>
+      </c>
+      <c r="J7" s="18">
+        <f t="shared" si="4"/>
+        <v>75000</v>
+      </c>
+      <c r="K7" s="18">
+        <f t="shared" si="5"/>
+        <v>15000</v>
+      </c>
+      <c r="L7" s="19">
+        <f t="shared" si="6"/>
+        <v>375000</v>
+      </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
@@ -955,13 +1038,34 @@
       <c r="E8" s="20">
         <v>45092</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="19"/>
+      <c r="F8" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - SURABAYA</v>
+      </c>
+      <c r="G8" s="17">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+      <c r="H8" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>VIP</v>
+      </c>
+      <c r="I8" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET A</v>
+      </c>
+      <c r="J8" s="18">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="K8" s="18">
+        <f t="shared" si="5"/>
+        <v>60000</v>
+      </c>
+      <c r="L8" s="19">
+        <f t="shared" si="6"/>
+        <v>500000</v>
+      </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
@@ -976,13 +1080,34 @@
       <c r="E9" s="20">
         <v>45093</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="19"/>
+      <c r="F9" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - SURABAYA</v>
+      </c>
+      <c r="G9" s="17">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+      <c r="H9" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>VIP</v>
+      </c>
+      <c r="I9" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET B</v>
+      </c>
+      <c r="J9" s="18">
+        <f t="shared" si="4"/>
+        <v>75000</v>
+      </c>
+      <c r="K9" s="18">
+        <f t="shared" si="5"/>
+        <v>60000</v>
+      </c>
+      <c r="L9" s="19">
+        <f t="shared" si="6"/>
+        <v>475000</v>
+      </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
@@ -997,13 +1122,34 @@
       <c r="E10" s="20">
         <v>45098</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="19"/>
+      <c r="F10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - BALI</v>
+      </c>
+      <c r="G10" s="17">
+        <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
+      <c r="H10" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>BISNIS</v>
+      </c>
+      <c r="I10" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET A</v>
+      </c>
+      <c r="J10" s="18">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="K10" s="18">
+        <f t="shared" si="5"/>
+        <v>60000</v>
+      </c>
+      <c r="L10" s="19">
+        <f t="shared" si="6"/>
+        <v>700000</v>
+      </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
@@ -1018,13 +1164,34 @@
       <c r="E11" s="20">
         <v>45098</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
+      <c r="F11" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - BALI</v>
+      </c>
+      <c r="G11" s="17">
+        <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
+      <c r="H11" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>BISNIS</v>
+      </c>
+      <c r="I11" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET C</v>
+      </c>
+      <c r="J11" s="18">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="K11" s="18">
+        <f t="shared" si="5"/>
+        <v>60000</v>
+      </c>
+      <c r="L11" s="19">
+        <f t="shared" si="6"/>
+        <v>650000</v>
+      </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
@@ -1039,13 +1206,34 @@
       <c r="E12" s="20">
         <v>45118</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="19"/>
+      <c r="F12" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - MEDAN</v>
+      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="1"/>
+        <v>500000</v>
+      </c>
+      <c r="H12" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>VIP</v>
+      </c>
+      <c r="I12" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET A</v>
+      </c>
+      <c r="J12" s="18">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="K12" s="18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="19">
+        <f t="shared" si="6"/>
+        <v>600000</v>
+      </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
@@ -1060,13 +1248,34 @@
       <c r="E13" s="20">
         <v>45119</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="19"/>
+      <c r="F13" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>JAKARTA - MEDAN</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="1"/>
+        <v>500000</v>
+      </c>
+      <c r="H13" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>VIP</v>
+      </c>
+      <c r="I13" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET C</v>
+      </c>
+      <c r="J13" s="18">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="K13" s="18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="19">
+        <f t="shared" si="6"/>
+        <v>550000</v>
+      </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="24" t="s">
@@ -1081,7 +1290,10 @@
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="25"/>
-      <c r="L14" s="19"/>
+      <c r="L14" s="19">
+        <f>SUM(L4:L13)</f>
+        <v>5350000</v>
+      </c>
     </row>
     <row r="15" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
@@ -1256,7 +1468,7 @@
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1" xr:uid="{24D3333E-935D-48D8-B0A3-622B577D0147}"/>
+    <hyperlink ref="E1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId2"/>

--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 1.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 1.xlsx
@@ -1290,10 +1290,7 @@
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="25"/>
-      <c r="L14" s="19">
-        <f>SUM(L4:L13)</f>
-        <v>5350000</v>
-      </c>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">

--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 1.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 1.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07137AAE-3105-48A0-916D-CDF463912086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -225,7 +226,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -490,9 +491,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -530,9 +531,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -567,7 +568,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -602,7 +603,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -775,7 +776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -870,34 +871,13 @@
       <c r="E4" s="20">
         <v>45048</v>
       </c>
-      <c r="F4" s="17" t="str">
-        <f>VLOOKUP(LEFT(C4,3),$C$17:$E$21,2,FALSE)</f>
-        <v>JAKARTA - SURABAYA</v>
-      </c>
-      <c r="G4" s="17">
-        <f>VLOOKUP(LEFT(C4,3),$C$17:$E$21,3,FALSE)</f>
-        <v>400000</v>
-      </c>
-      <c r="H4" s="17" t="str">
-        <f>INDEX($F$17:$F$20,MATCH(MID(C4,4,1),$G$17:$G$20,0),0)</f>
-        <v>BISNIS</v>
-      </c>
-      <c r="I4" s="18" t="str">
-        <f>HLOOKUP(MID(C4,6,2),$I$17:$L$19,2,FALSE)</f>
-        <v>PAKET A</v>
-      </c>
-      <c r="J4" s="18">
-        <f>HLOOKUP(MID(C4,6,2),$I$17:$L$19,3,FALSE)</f>
-        <v>100000</v>
-      </c>
-      <c r="K4" s="18">
-        <f>IF($E$2-E4&gt;30,INDEX($H$17:$H$20,MATCH(H4,$F$17:$F$20,0))*G4,0)</f>
-        <v>40000</v>
-      </c>
-      <c r="L4" s="19">
-        <f>G4+J4-M4</f>
-        <v>500000</v>
-      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="19"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
@@ -912,34 +892,13 @@
       <c r="E5" s="20">
         <v>45051</v>
       </c>
-      <c r="F5" s="17" t="str">
-        <f t="shared" ref="F5:F13" si="0">VLOOKUP(LEFT(C5,3),$C$17:$E$21,2,FALSE)</f>
-        <v>JAKARTA - BALI</v>
-      </c>
-      <c r="G5" s="17">
-        <f t="shared" ref="G5:G13" si="1">VLOOKUP(LEFT(C5,3),$C$17:$E$21,3,FALSE)</f>
-        <v>600000</v>
-      </c>
-      <c r="H5" s="17" t="str">
-        <f t="shared" ref="H5:H13" si="2">INDEX($F$17:$F$20,MATCH(MID(C5,4,1),$G$17:$G$20,0),0)</f>
-        <v>BISNIS</v>
-      </c>
-      <c r="I5" s="18" t="str">
-        <f t="shared" ref="I5:I13" si="3">HLOOKUP(MID(C5,6,2),$I$17:$L$19,2,FALSE)</f>
-        <v>PAKET C</v>
-      </c>
-      <c r="J5" s="18">
-        <f t="shared" ref="J5:J13" si="4">HLOOKUP(MID(C5,6,2),$I$17:$L$19,3,FALSE)</f>
-        <v>50000</v>
-      </c>
-      <c r="K5" s="18">
-        <f t="shared" ref="K5:K13" si="5">IF($E$2-E5&gt;30,INDEX($H$17:$H$20,MATCH(H5,$F$17:$F$20,0))*G5,0)</f>
-        <v>60000</v>
-      </c>
-      <c r="L5" s="19">
-        <f t="shared" ref="L5:L13" si="6">G5+J5-M5</f>
-        <v>650000</v>
-      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
@@ -954,34 +913,13 @@
       <c r="E6" s="20">
         <v>45057</v>
       </c>
-      <c r="F6" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - BANDUNG</v>
-      </c>
-      <c r="G6" s="17">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-      <c r="H6" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>EKONOMI</v>
-      </c>
-      <c r="I6" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET C</v>
-      </c>
-      <c r="J6" s="18">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
-      <c r="K6" s="18">
-        <f t="shared" si="5"/>
-        <v>15000</v>
-      </c>
-      <c r="L6" s="19">
-        <f t="shared" si="6"/>
-        <v>350000</v>
-      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -996,34 +934,13 @@
       <c r="E7" s="20">
         <v>45059</v>
       </c>
-      <c r="F7" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - BANDUNG</v>
-      </c>
-      <c r="G7" s="17">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-      <c r="H7" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>EKONOMI</v>
-      </c>
-      <c r="I7" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET B</v>
-      </c>
-      <c r="J7" s="18">
-        <f t="shared" si="4"/>
-        <v>75000</v>
-      </c>
-      <c r="K7" s="18">
-        <f t="shared" si="5"/>
-        <v>15000</v>
-      </c>
-      <c r="L7" s="19">
-        <f t="shared" si="6"/>
-        <v>375000</v>
-      </c>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
@@ -1038,34 +955,13 @@
       <c r="E8" s="20">
         <v>45092</v>
       </c>
-      <c r="F8" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - SURABAYA</v>
-      </c>
-      <c r="G8" s="17">
-        <f t="shared" si="1"/>
-        <v>400000</v>
-      </c>
-      <c r="H8" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>VIP</v>
-      </c>
-      <c r="I8" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET A</v>
-      </c>
-      <c r="J8" s="18">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-      <c r="K8" s="18">
-        <f t="shared" si="5"/>
-        <v>60000</v>
-      </c>
-      <c r="L8" s="19">
-        <f t="shared" si="6"/>
-        <v>500000</v>
-      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
@@ -1080,34 +976,13 @@
       <c r="E9" s="20">
         <v>45093</v>
       </c>
-      <c r="F9" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - SURABAYA</v>
-      </c>
-      <c r="G9" s="17">
-        <f t="shared" si="1"/>
-        <v>400000</v>
-      </c>
-      <c r="H9" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>VIP</v>
-      </c>
-      <c r="I9" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET B</v>
-      </c>
-      <c r="J9" s="18">
-        <f t="shared" si="4"/>
-        <v>75000</v>
-      </c>
-      <c r="K9" s="18">
-        <f t="shared" si="5"/>
-        <v>60000</v>
-      </c>
-      <c r="L9" s="19">
-        <f t="shared" si="6"/>
-        <v>475000</v>
-      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
@@ -1122,34 +997,13 @@
       <c r="E10" s="20">
         <v>45098</v>
       </c>
-      <c r="F10" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - BALI</v>
-      </c>
-      <c r="G10" s="17">
-        <f t="shared" si="1"/>
-        <v>600000</v>
-      </c>
-      <c r="H10" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>BISNIS</v>
-      </c>
-      <c r="I10" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET A</v>
-      </c>
-      <c r="J10" s="18">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-      <c r="K10" s="18">
-        <f t="shared" si="5"/>
-        <v>60000</v>
-      </c>
-      <c r="L10" s="19">
-        <f t="shared" si="6"/>
-        <v>700000</v>
-      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
@@ -1164,34 +1018,13 @@
       <c r="E11" s="20">
         <v>45098</v>
       </c>
-      <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - BALI</v>
-      </c>
-      <c r="G11" s="17">
-        <f t="shared" si="1"/>
-        <v>600000</v>
-      </c>
-      <c r="H11" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>BISNIS</v>
-      </c>
-      <c r="I11" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET C</v>
-      </c>
-      <c r="J11" s="18">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
-      <c r="K11" s="18">
-        <f t="shared" si="5"/>
-        <v>60000</v>
-      </c>
-      <c r="L11" s="19">
-        <f t="shared" si="6"/>
-        <v>650000</v>
-      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
@@ -1206,34 +1039,13 @@
       <c r="E12" s="20">
         <v>45118</v>
       </c>
-      <c r="F12" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - MEDAN</v>
-      </c>
-      <c r="G12" s="17">
-        <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-      <c r="H12" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>VIP</v>
-      </c>
-      <c r="I12" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET A</v>
-      </c>
-      <c r="J12" s="18">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-      <c r="K12" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="19">
-        <f t="shared" si="6"/>
-        <v>600000</v>
-      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
@@ -1248,34 +1060,13 @@
       <c r="E13" s="20">
         <v>45119</v>
       </c>
-      <c r="F13" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>JAKARTA - MEDAN</v>
-      </c>
-      <c r="G13" s="17">
-        <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-      <c r="H13" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>VIP</v>
-      </c>
-      <c r="I13" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET C</v>
-      </c>
-      <c r="J13" s="18">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
-      <c r="K13" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="19">
-        <f t="shared" si="6"/>
-        <v>550000</v>
-      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="24" t="s">
@@ -1465,7 +1256,7 @@
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1"/>
+    <hyperlink ref="E1" r:id="rId1" xr:uid="{24D3333E-935D-48D8-B0A3-622B577D0147}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId2"/>
